--- a/tests/fixtures/CRX10iA-solutions.xlsx
+++ b/tests/fixtures/CRX10iA-solutions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\francois.fournier\Git\temp\tests\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\francois.fournier\Git\robodk_crx_kinematics\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F31DF59-1E84-4039-B44E-75BCE1F1DC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51801F44-5951-460F-8035-1AE86ED66FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{72AB75B4-E23B-4100-82C4-9E64ADA72CB5}"/>
+    <workbookView xWindow="29580" yWindow="-4755" windowWidth="38700" windowHeight="15345" xr2:uid="{72AB75B4-E23B-4100-82C4-9E64ADA72CB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="43">
   <si>
     <t>N</t>
   </si>
@@ -142,6 +142,30 @@
   <si>
     <t>PERCH</t>
   </si>
+  <si>
+    <t>COUPLING1</t>
+  </si>
+  <si>
+    <t>COUPLING2</t>
+  </si>
+  <si>
+    <t>COUPLING3</t>
+  </si>
+  <si>
+    <t>COUPLING4</t>
+  </si>
+  <si>
+    <t>COUPLING5</t>
+  </si>
+  <si>
+    <t>COUPLING6</t>
+  </si>
+  <si>
+    <t>COUPLING7</t>
+  </si>
+  <si>
+    <t>COUPLING8</t>
+  </si>
 </sst>
 </file>
 
@@ -150,10 +174,15 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -289,8 +318,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2658E89C-6CD6-4DBF-825E-4C46162D9E29}" name="Table1" displayName="Table1" ref="A1:R65" totalsRowShown="0">
-  <autoFilter ref="A1:R65" xr:uid="{2658E89C-6CD6-4DBF-825E-4C46162D9E29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2658E89C-6CD6-4DBF-825E-4C46162D9E29}" name="Table1" displayName="Table1" ref="A1:R73" totalsRowShown="0">
+  <autoFilter ref="A1:R73" xr:uid="{2658E89C-6CD6-4DBF-825E-4C46162D9E29}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R65">
     <sortCondition ref="A1:A65"/>
   </sortState>
@@ -635,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E446534-5465-489F-9830-23FECF10CEB6}">
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.25" bestFit="1" customWidth="1"/>
@@ -4295,7 +4324,456 @@
         <v>16</v>
       </c>
     </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>12</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" s="1">
+        <v>600</v>
+      </c>
+      <c r="D66" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E66" s="1">
+        <v>540</v>
+      </c>
+      <c r="F66" s="1">
+        <v>-180</v>
+      </c>
+      <c r="G66" s="1">
+        <v>-90</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
+        <v>-10.663</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="L66" s="3">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3">
+        <v>-0.99</v>
+      </c>
+      <c r="N66" s="4">
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
+        <v>0</v>
+      </c>
+      <c r="P66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>2</v>
+      </c>
+      <c r="R66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>13</v>
+      </c>
+      <c r="B67" t="s">
+        <v>36</v>
+      </c>
+      <c r="C67" s="1">
+        <v>800</v>
+      </c>
+      <c r="D67" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E67" s="1">
+        <v>540</v>
+      </c>
+      <c r="F67" s="1">
+        <v>180</v>
+      </c>
+      <c r="G67" s="1">
+        <v>-90</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
+        <v>10.680999999999999</v>
+      </c>
+      <c r="K67" s="3">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="L67" s="3">
+        <v>0</v>
+      </c>
+      <c r="M67" s="3">
+        <v>-0.99299999999999999</v>
+      </c>
+      <c r="N67" s="4">
+        <v>0</v>
+      </c>
+      <c r="O67" t="s">
+        <v>0</v>
+      </c>
+      <c r="P67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>2</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>14</v>
+      </c>
+      <c r="B68" t="s">
+        <v>37</v>
+      </c>
+      <c r="C68" s="1">
+        <v>793.77</v>
+      </c>
+      <c r="D68" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E68" s="1">
+        <v>531.79600000000005</v>
+      </c>
+      <c r="F68" s="1">
+        <v>180</v>
+      </c>
+      <c r="G68" s="1">
+        <v>-90</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3">
+        <v>10</v>
+      </c>
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="4">
+        <v>0</v>
+      </c>
+      <c r="O68" t="s">
+        <v>0</v>
+      </c>
+      <c r="P68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>2</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="1">
+        <v>606.23</v>
+      </c>
+      <c r="D69" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E69" s="1">
+        <v>531.79600000000005</v>
+      </c>
+      <c r="F69" s="1">
+        <v>180</v>
+      </c>
+      <c r="G69" s="1">
+        <v>-90</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>-10</v>
+      </c>
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="4">
+        <v>0</v>
+      </c>
+      <c r="O69" t="s">
+        <v>0</v>
+      </c>
+      <c r="P69" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>2</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>16</v>
+      </c>
+      <c r="B70" t="s">
+        <v>39</v>
+      </c>
+      <c r="C70" s="1">
+        <v>783.13499999999999</v>
+      </c>
+      <c r="D70" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E70" s="1">
+        <v>653.35</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>-80</v>
+      </c>
+      <c r="H70" s="1">
+        <v>180</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>10</v>
+      </c>
+      <c r="K70" s="3">
+        <v>10</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="4">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>0</v>
+      </c>
+      <c r="P70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>2</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>17</v>
+      </c>
+      <c r="B71" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" s="1">
+        <v>783.13499999999999</v>
+      </c>
+      <c r="D71" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E71" s="1">
+        <v>410.24200000000002</v>
+      </c>
+      <c r="F71" s="1">
+        <v>180</v>
+      </c>
+      <c r="G71" s="1">
+        <v>-80</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3">
+        <v>10</v>
+      </c>
+      <c r="K71" s="3">
+        <v>-10</v>
+      </c>
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="4">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>0</v>
+      </c>
+      <c r="P71" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>2</v>
+      </c>
+      <c r="R71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>18</v>
+      </c>
+      <c r="B72" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="1">
+        <v>595.59500000000003</v>
+      </c>
+      <c r="D72" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E72" s="1">
+        <v>653.35</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>-80</v>
+      </c>
+      <c r="H72" s="1">
+        <v>180</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-10</v>
+      </c>
+      <c r="K72" s="3">
+        <v>10</v>
+      </c>
+      <c r="L72" s="3">
+        <v>0</v>
+      </c>
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="4">
+        <v>0</v>
+      </c>
+      <c r="O72" t="s">
+        <v>0</v>
+      </c>
+      <c r="P72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>2</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>19</v>
+      </c>
+      <c r="B73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="1">
+        <v>595.59500000000003</v>
+      </c>
+      <c r="D73" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E73" s="1">
+        <v>410.24200000000002</v>
+      </c>
+      <c r="F73" s="1">
+        <v>180</v>
+      </c>
+      <c r="G73" s="1">
+        <v>-80</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <v>-10</v>
+      </c>
+      <c r="K73" s="3">
+        <v>-10</v>
+      </c>
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="4">
+        <v>0</v>
+      </c>
+      <c r="O73" t="s">
+        <v>0</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>2</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/tests/fixtures/CRX10iA-solutions.xlsx
+++ b/tests/fixtures/CRX10iA-solutions.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\francois.fournier\Git\robodk_crx_kinematics\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51801F44-5951-460F-8035-1AE86ED66FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF8BDCA-AAF1-4D3C-BA63-F7EB0895A923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="-4755" windowWidth="38700" windowHeight="15345" xr2:uid="{72AB75B4-E23B-4100-82C4-9E64ADA72CB5}"/>
+    <workbookView xWindow="54495" yWindow="-5535" windowWidth="26010" windowHeight="20985" xr2:uid="{72AB75B4-E23B-4100-82C4-9E64ADA72CB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="75">
   <si>
     <t>N</t>
   </si>
@@ -113,12 +114,6 @@
     <t>HOME</t>
   </si>
   <si>
-    <t>FORWARD</t>
-  </si>
-  <si>
-    <t>CANDLE</t>
-  </si>
-  <si>
     <t>ALL8</t>
   </si>
   <si>
@@ -165,6 +160,108 @@
   </si>
   <si>
     <t>COUPLING8</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>q1_deg</t>
+  </si>
+  <si>
+    <t>q2_deg</t>
+  </si>
+  <si>
+    <t>q3_deg</t>
+  </si>
+  <si>
+    <t>q4_deg</t>
+  </si>
+  <si>
+    <t>q5_deg</t>
+  </si>
+  <si>
+    <t>q6_deg</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>wrist_sing_q5=0</t>
+  </si>
+  <si>
+    <t>wrist_near_q5=+1e-6rad</t>
+  </si>
+  <si>
+    <t>wrist_near_q5=-1e-6rad</t>
+  </si>
+  <si>
+    <t>wrist_near_q5=+1e-3rad</t>
+  </si>
+  <si>
+    <t>wrist_near_q5=-1e-3rad</t>
+  </si>
+  <si>
+    <t>wrist_sing_q5=180</t>
+  </si>
+  <si>
+    <t>wrist_near_q5=pi+1e-3rad</t>
+  </si>
+  <si>
+    <t>wrist_near_q5=pi-1e-3rad</t>
+  </si>
+  <si>
+    <t>elbow_sing_q3=90</t>
+  </si>
+  <si>
+    <t>elbow_near_q3=90+1e-3rad</t>
+  </si>
+  <si>
+    <t>elbow_near_q3=90-1e-3rad</t>
+  </si>
+  <si>
+    <t>elbow_sing_q3=-90</t>
+  </si>
+  <si>
+    <t>elbow_near_q3=-90+1e-3rad</t>
+  </si>
+  <si>
+    <t>elbow_near_q3=-90-1e-3rad</t>
+  </si>
+  <si>
+    <t>stacked_sing_q3=90_q5=0</t>
+  </si>
+  <si>
+    <t>stacked_sing_q3=-90_q5=180</t>
+  </si>
+  <si>
+    <t>stacked_near_q3=90-1e-3rad_q5=+1e-3rad</t>
+  </si>
+  <si>
+    <t>stacked_near_q3=-90+1e-3rad_q5=pi-1e-3rad</t>
+  </si>
+  <si>
+    <t>MAX_X</t>
+  </si>
+  <si>
+    <t>MIN_X</t>
+  </si>
+  <si>
+    <t>MAX_Y</t>
+  </si>
+  <si>
+    <t>MIN_Y</t>
+  </si>
+  <si>
+    <t>MAX_Z</t>
+  </si>
+  <si>
+    <t>MIN_Z</t>
+  </si>
+  <si>
+    <t>WRIST_SING</t>
+  </si>
+  <si>
+    <t>WRIST_SING_NEAR_RG_LIMIT</t>
   </si>
 </sst>
 </file>
@@ -318,10 +415,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2658E89C-6CD6-4DBF-825E-4C46162D9E29}" name="Table1" displayName="Table1" ref="A1:R73" totalsRowShown="0">
-  <autoFilter ref="A1:R73" xr:uid="{2658E89C-6CD6-4DBF-825E-4C46162D9E29}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R65">
-    <sortCondition ref="A1:A65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2658E89C-6CD6-4DBF-825E-4C46162D9E29}" name="Table1" displayName="Table1" ref="A1:R84" totalsRowShown="0">
+  <autoFilter ref="A1:R84" xr:uid="{2658E89C-6CD6-4DBF-825E-4C46162D9E29}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R69">
+    <sortCondition ref="A1:A69"/>
   </sortState>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{0738EC40-35D7-4B20-94D2-83C08F2EBF72}" name="TEST CASE"/>
@@ -664,20 +761,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E446534-5465-489F-9830-23FECF10CEB6}">
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="8" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="8.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="2" customWidth="1"/>
+    <col min="10" max="13" width="8.25" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.25" style="4" customWidth="1"/>
     <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="5.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
@@ -913,7 +1005,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C5" s="1">
         <v>1240</v>
@@ -969,34 +1061,34 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>-1240</v>
       </c>
       <c r="D6" s="1">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="E6" s="1">
-        <v>1240</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="H6" s="1">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J6" s="3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K6" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
@@ -1014,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -1025,46 +1117,46 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1">
-        <v>150</v>
+        <v>1240</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="H7" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J7" s="3">
-        <v>28.797000000000001</v>
+        <v>90</v>
       </c>
       <c r="K7" s="3">
-        <v>-35.453000000000003</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="M7" s="3">
-        <v>54.546999999999997</v>
+        <v>0</v>
       </c>
       <c r="N7" s="4">
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P7" t="s">
         <v>1</v>
@@ -1078,217 +1170,199 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1">
-        <v>700</v>
+        <v>-150</v>
       </c>
       <c r="D8" s="1">
-        <v>150</v>
+        <v>-1240</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="H8" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>-155.81100000000001</v>
+        <v>-90</v>
       </c>
       <c r="J8" s="3">
-        <v>-125.453</v>
+        <v>90</v>
       </c>
       <c r="K8" s="3">
-        <v>118.797</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>-151.203</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>155.81100000000001</v>
-      </c>
-      <c r="O8" t="s">
-        <v>0</v>
-      </c>
-      <c r="P8" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C9" s="1">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>150</v>
+        <v>-150</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>1240</v>
       </c>
       <c r="F9" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>180</v>
+        <v>-180</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>125.453</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>61.203000000000003</v>
+        <v>90</v>
       </c>
       <c r="L9" s="3">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>151.203</v>
+        <v>0</v>
       </c>
       <c r="N9" s="4">
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C10" s="1">
-        <v>700</v>
+        <v>9.4E-2</v>
       </c>
       <c r="D10" s="1">
-        <v>150</v>
+        <v>-150</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>-1240</v>
       </c>
       <c r="F10" s="1">
-        <v>180</v>
+        <v>-180</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>-155.81100000000001</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>-28.797000000000001</v>
+        <v>179.99</v>
       </c>
       <c r="K10" s="3">
-        <v>215.453</v>
+        <v>-90</v>
       </c>
       <c r="L10" s="3">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>-54.546999999999997</v>
+        <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>155.81100000000001</v>
-      </c>
-      <c r="O10" t="s">
-        <v>0</v>
-      </c>
-      <c r="P10" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1">
         <v>700</v>
       </c>
       <c r="D11" s="1">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="E11" s="1">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1">
         <v>180</v>
       </c>
       <c r="G11" s="1">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="3">
-        <v>0</v>
+        <v>28.797000000000001</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>-35.453000000000003</v>
       </c>
       <c r="L11" s="3">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="M11" s="3">
-        <v>0</v>
+        <v>54.546999999999997</v>
       </c>
       <c r="N11" s="4">
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P11" t="s">
         <v>1</v>
@@ -1302,55 +1376,55 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>700</v>
       </c>
       <c r="D12" s="1">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="E12" s="1">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
         <v>180</v>
       </c>
       <c r="G12" s="1">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>-155.81100000000001</v>
       </c>
       <c r="J12" s="3">
-        <v>90</v>
+        <v>-125.453</v>
       </c>
       <c r="K12" s="3">
-        <v>90</v>
+        <v>118.797</v>
       </c>
       <c r="L12" s="3">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="M12" s="3">
-        <v>-90</v>
+        <v>-151.203</v>
       </c>
       <c r="N12" s="4">
-        <v>0</v>
+        <v>155.81100000000001</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R12">
         <v>2</v>
@@ -1358,43 +1432,43 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1">
-        <v>380</v>
+        <v>700</v>
       </c>
       <c r="D13" s="1">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="E13" s="1">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1">
+        <v>180</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>180</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>125.453</v>
+      </c>
+      <c r="K13" s="3">
+        <v>61.203000000000003</v>
+      </c>
+      <c r="L13" s="3">
         <v>-180</v>
       </c>
-      <c r="G13" s="1">
-        <v>90</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <v>90</v>
-      </c>
-      <c r="K13" s="3">
-        <v>90</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
       <c r="M13" s="3">
-        <v>90</v>
+        <v>151.203</v>
       </c>
       <c r="N13" s="4">
         <v>0</v>
@@ -1409,51 +1483,51 @@
         <v>2</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1">
-        <v>380</v>
+        <v>700</v>
       </c>
       <c r="D14" s="1">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="E14" s="1">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1">
+        <v>180</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>180</v>
+      </c>
+      <c r="I14" s="2">
+        <v>-155.81100000000001</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-28.797000000000001</v>
+      </c>
+      <c r="K14" s="3">
+        <v>215.453</v>
+      </c>
+      <c r="L14" s="3">
         <v>-180</v>
       </c>
-      <c r="G14" s="1">
-        <v>90</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>-29.024999999999999</v>
-      </c>
-      <c r="J14" s="3">
-        <v>90.524000000000001</v>
-      </c>
-      <c r="K14" s="3">
-        <v>81.739999999999995</v>
-      </c>
-      <c r="L14" s="3">
-        <v>150.721</v>
-      </c>
       <c r="M14" s="3">
-        <v>-97.216999999999999</v>
+        <v>-54.546999999999997</v>
       </c>
       <c r="N14" s="4">
-        <v>175.971</v>
+        <v>155.81100000000001</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
@@ -1462,54 +1536,54 @@
         <v>20</v>
       </c>
       <c r="Q14" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1">
-        <v>120.929</v>
+        <v>700</v>
       </c>
       <c r="D15" s="1">
-        <v>-304.29000000000002</v>
+        <v>-150</v>
       </c>
       <c r="E15" s="1">
-        <v>523.66099999999994</v>
+        <v>540</v>
       </c>
       <c r="F15" s="1">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G15" s="1">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>-53.304000000000002</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>-41.707000000000001</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>-3.0659999999999998</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>94.105000000000004</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>-36.805999999999997</v>
+        <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>84.878</v>
+        <v>0</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
@@ -1526,52 +1600,52 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1">
-        <v>120.929</v>
+        <v>700</v>
       </c>
       <c r="D16" s="1">
-        <v>-304.29000000000002</v>
+        <v>-150</v>
       </c>
       <c r="E16" s="1">
-        <v>523.66099999999994</v>
+        <v>540</v>
       </c>
       <c r="F16" s="1">
+        <v>180</v>
+      </c>
+      <c r="G16" s="1">
+        <v>-90</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
         <v>90</v>
       </c>
-      <c r="G16" s="1">
+      <c r="K16" s="3">
         <v>90</v>
       </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>-94.524000000000001</v>
-      </c>
-      <c r="J16" s="3">
-        <v>-46.154000000000003</v>
-      </c>
-      <c r="K16" s="3">
-        <v>8.4109999999999996</v>
-      </c>
       <c r="L16" s="3">
-        <v>151.58799999999999</v>
+        <v>0</v>
       </c>
       <c r="M16" s="3">
-        <v>9.5429999999999993</v>
+        <v>-90</v>
       </c>
       <c r="N16" s="4">
-        <v>28.079000000000001</v>
+        <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q16" t="s">
         <v>2</v>
@@ -1582,22 +1656,22 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="1">
-        <v>120.929</v>
+        <v>380</v>
       </c>
       <c r="D17" s="1">
-        <v>-304.29000000000002</v>
+        <v>-150</v>
       </c>
       <c r="E17" s="1">
-        <v>523.66099999999994</v>
+        <v>540</v>
       </c>
       <c r="F17" s="1">
-        <v>90</v>
+        <v>-180</v>
       </c>
       <c r="G17" s="1">
         <v>90</v>
@@ -1606,25 +1680,25 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>-29.111000000000001</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
-        <v>79.789000000000001</v>
+        <v>90</v>
       </c>
       <c r="K17" s="3">
-        <v>115.78</v>
+        <v>90</v>
       </c>
       <c r="L17" s="3">
-        <v>63.37</v>
+        <v>0</v>
       </c>
       <c r="M17" s="3">
-        <v>-102.215</v>
+        <v>90</v>
       </c>
       <c r="N17" s="4">
-        <v>-157.12100000000001</v>
+        <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P17" t="s">
         <v>20</v>
@@ -1633,27 +1707,27 @@
         <v>2</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="1">
-        <v>120.929</v>
+        <v>380</v>
       </c>
       <c r="D18" s="1">
-        <v>-304.29000000000002</v>
+        <v>-150</v>
       </c>
       <c r="E18" s="1">
-        <v>523.66099999999994</v>
+        <v>540</v>
       </c>
       <c r="F18" s="1">
-        <v>90</v>
+        <v>-180</v>
       </c>
       <c r="G18" s="1">
         <v>90</v>
@@ -1662,25 +1736,25 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>-100.556</v>
+        <v>-29.024999999999999</v>
       </c>
       <c r="J18" s="3">
-        <v>73.206000000000003</v>
+        <v>90.524000000000001</v>
       </c>
       <c r="K18" s="3">
-        <v>133.27799999999999</v>
+        <v>81.739999999999995</v>
       </c>
       <c r="L18" s="3">
-        <v>165.642</v>
+        <v>150.721</v>
       </c>
       <c r="M18" s="3">
-        <v>132.37200000000001</v>
+        <v>-97.216999999999999</v>
       </c>
       <c r="N18" s="4">
-        <v>-9.7880000000000003</v>
+        <v>175.971</v>
       </c>
       <c r="O18" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P18" t="s">
         <v>20</v>
@@ -1689,15 +1763,15 @@
         <v>2</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C19" s="1">
         <v>120.929</v>
@@ -1718,22 +1792,22 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>150.88900000000001</v>
+        <v>-53.304000000000002</v>
       </c>
       <c r="J19" s="3">
-        <v>-79.789000000000001</v>
+        <v>-41.707000000000001</v>
       </c>
       <c r="K19" s="3">
-        <v>64.22</v>
+        <v>-3.0659999999999998</v>
       </c>
       <c r="L19" s="3">
-        <v>-116.63</v>
+        <v>94.105000000000004</v>
       </c>
       <c r="M19" s="3">
-        <v>-102.215</v>
+        <v>-36.805999999999997</v>
       </c>
       <c r="N19" s="4">
-        <v>-157.12100000000001</v>
+        <v>84.878</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
@@ -1742,18 +1816,18 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="1">
         <v>120.929</v>
@@ -1774,22 +1848,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>79.444000000000003</v>
+        <v>-94.524000000000001</v>
       </c>
       <c r="J20" s="3">
-        <v>-73.206000000000003</v>
+        <v>-46.154000000000003</v>
       </c>
       <c r="K20" s="3">
-        <v>46.722000000000001</v>
+        <v>8.4109999999999996</v>
       </c>
       <c r="L20" s="3">
-        <v>-14.358000000000001</v>
+        <v>151.58799999999999</v>
       </c>
       <c r="M20" s="3">
-        <v>132.37200000000001</v>
+        <v>9.5429999999999993</v>
       </c>
       <c r="N20" s="4">
-        <v>-9.7880000000000003</v>
+        <v>28.079000000000001</v>
       </c>
       <c r="O20" t="s">
         <v>18</v>
@@ -1798,18 +1872,18 @@
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21" s="1">
         <v>120.929</v>
@@ -1830,42 +1904,42 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>85.475999999999999</v>
+        <v>-29.111000000000001</v>
       </c>
       <c r="J21" s="3">
-        <v>46.154000000000003</v>
+        <v>79.789000000000001</v>
       </c>
       <c r="K21" s="3">
-        <v>171.589</v>
+        <v>115.78</v>
       </c>
       <c r="L21" s="3">
-        <v>-28.411999999999999</v>
+        <v>63.37</v>
       </c>
       <c r="M21" s="3">
-        <v>9.5429999999999993</v>
+        <v>-102.215</v>
       </c>
       <c r="N21" s="4">
-        <v>28.079000000000001</v>
+        <v>-157.12100000000001</v>
       </c>
       <c r="O21" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P21" t="s">
         <v>20</v>
       </c>
       <c r="Q21" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R21">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C22" s="1">
         <v>120.929</v>
@@ -1886,78 +1960,78 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>126.696</v>
+        <v>-100.556</v>
       </c>
       <c r="J22" s="3">
-        <v>41.707000000000001</v>
+        <v>73.206000000000003</v>
       </c>
       <c r="K22" s="3">
-        <v>183.066</v>
+        <v>133.27799999999999</v>
       </c>
       <c r="L22" s="3">
-        <v>-85.894999999999996</v>
+        <v>165.642</v>
       </c>
       <c r="M22" s="3">
-        <v>-36.805999999999997</v>
+        <v>132.37200000000001</v>
       </c>
       <c r="N22" s="4">
-        <v>84.878</v>
+        <v>-9.7880000000000003</v>
       </c>
       <c r="O22" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P22" t="s">
         <v>20</v>
       </c>
       <c r="Q22" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C23" s="1">
-        <v>119.878</v>
+        <v>120.929</v>
       </c>
       <c r="D23" s="1">
-        <v>289.12299999999999</v>
+        <v>-304.29000000000002</v>
       </c>
       <c r="E23" s="1">
-        <v>498.44400000000002</v>
+        <v>523.66099999999994</v>
       </c>
       <c r="F23" s="1">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G23" s="1">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>94.201999999999998</v>
+        <v>150.88900000000001</v>
       </c>
       <c r="J23" s="3">
-        <v>-48.81</v>
+        <v>-79.789000000000001</v>
       </c>
       <c r="K23" s="3">
-        <v>7.117</v>
+        <v>64.22</v>
       </c>
       <c r="L23" s="3">
-        <v>30.67</v>
+        <v>-116.63</v>
       </c>
       <c r="M23" s="3">
-        <v>-8.2590000000000003</v>
+        <v>-102.215</v>
       </c>
       <c r="N23" s="4">
-        <v>-30.408999999999999</v>
+        <v>-157.12100000000001</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
@@ -1966,54 +2040,54 @@
         <v>1</v>
       </c>
       <c r="Q23" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1">
-        <v>119.878</v>
+        <v>120.929</v>
       </c>
       <c r="D24" s="1">
-        <v>289.12299999999999</v>
+        <v>-304.29000000000002</v>
       </c>
       <c r="E24" s="1">
-        <v>498.44400000000002</v>
+        <v>523.66099999999994</v>
       </c>
       <c r="F24" s="1">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G24" s="1">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>51.69</v>
+        <v>79.444000000000003</v>
       </c>
       <c r="J24" s="3">
-        <v>-43.829000000000001</v>
+        <v>-73.206000000000003</v>
       </c>
       <c r="K24" s="3">
-        <v>-4.2530000000000001</v>
+        <v>46.722000000000001</v>
       </c>
       <c r="L24" s="3">
-        <v>84.637</v>
+        <v>-14.358000000000001</v>
       </c>
       <c r="M24" s="3">
-        <v>38.509</v>
+        <v>132.37200000000001</v>
       </c>
       <c r="N24" s="4">
-        <v>-83.159000000000006</v>
+        <v>-9.7880000000000003</v>
       </c>
       <c r="O24" t="s">
         <v>18</v>
@@ -2022,130 +2096,130 @@
         <v>1</v>
       </c>
       <c r="Q24" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C25" s="1">
-        <v>119.878</v>
+        <v>120.929</v>
       </c>
       <c r="D25" s="1">
-        <v>289.12299999999999</v>
+        <v>-304.29000000000002</v>
       </c>
       <c r="E25" s="1">
-        <v>498.44400000000002</v>
+        <v>523.66099999999994</v>
       </c>
       <c r="F25" s="1">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G25" s="1">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>101.78700000000001</v>
+        <v>85.475999999999999</v>
       </c>
       <c r="J25" s="3">
-        <v>73.668999999999997</v>
+        <v>46.154000000000003</v>
       </c>
       <c r="K25" s="3">
-        <v>135.67500000000001</v>
+        <v>171.589</v>
       </c>
       <c r="L25" s="3">
-        <v>16.628</v>
+        <v>-28.411999999999999</v>
       </c>
       <c r="M25" s="3">
-        <v>-134.45099999999999</v>
+        <v>9.5429999999999993</v>
       </c>
       <c r="N25" s="4">
-        <v>11.813000000000001</v>
+        <v>28.079000000000001</v>
       </c>
       <c r="O25" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P25" t="s">
         <v>20</v>
       </c>
       <c r="Q25" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R25">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1">
-        <v>119.878</v>
+        <v>120.929</v>
       </c>
       <c r="D26" s="1">
-        <v>289.12299999999999</v>
+        <v>-304.29000000000002</v>
       </c>
       <c r="E26" s="1">
-        <v>498.44400000000002</v>
+        <v>523.66099999999994</v>
       </c>
       <c r="F26" s="1">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G26" s="1">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>26.748999999999999</v>
+        <v>126.696</v>
       </c>
       <c r="J26" s="3">
-        <v>81.387</v>
+        <v>41.707000000000001</v>
       </c>
       <c r="K26" s="3">
-        <v>117.223</v>
+        <v>183.066</v>
       </c>
       <c r="L26" s="3">
-        <v>114.142</v>
+        <v>-85.894999999999996</v>
       </c>
       <c r="M26" s="3">
-        <v>101.88200000000001</v>
+        <v>-36.805999999999997</v>
       </c>
       <c r="N26" s="4">
-        <v>155.327</v>
+        <v>84.878</v>
       </c>
       <c r="O26" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P26" t="s">
         <v>20</v>
       </c>
       <c r="Q26" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1">
         <v>119.878</v>
@@ -2166,22 +2240,22 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>-78.212999999999994</v>
+        <v>94.201999999999998</v>
       </c>
       <c r="J27" s="3">
-        <v>-73.668999999999997</v>
+        <v>-48.81</v>
       </c>
       <c r="K27" s="3">
-        <v>44.325000000000003</v>
+        <v>7.117</v>
       </c>
       <c r="L27" s="3">
-        <v>-163.37200000000001</v>
+        <v>30.67</v>
       </c>
       <c r="M27" s="3">
-        <v>-134.45099999999999</v>
+        <v>-8.2590000000000003</v>
       </c>
       <c r="N27" s="4">
-        <v>11.813000000000001</v>
+        <v>-30.408999999999999</v>
       </c>
       <c r="O27" t="s">
         <v>0</v>
@@ -2190,18 +2264,18 @@
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C28" s="1">
         <v>119.878</v>
@@ -2222,22 +2296,22 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>-153.251</v>
+        <v>51.69</v>
       </c>
       <c r="J28" s="3">
-        <v>-81.387</v>
+        <v>-43.829000000000001</v>
       </c>
       <c r="K28" s="3">
-        <v>62.777000000000001</v>
+        <v>-4.2530000000000001</v>
       </c>
       <c r="L28" s="3">
-        <v>-65.858000000000004</v>
+        <v>84.637</v>
       </c>
       <c r="M28" s="3">
-        <v>101.88200000000001</v>
+        <v>38.509</v>
       </c>
       <c r="N28" s="4">
-        <v>155.327</v>
+        <v>-83.159000000000006</v>
       </c>
       <c r="O28" t="s">
         <v>18</v>
@@ -2246,18 +2320,18 @@
         <v>1</v>
       </c>
       <c r="Q28" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R28">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C29" s="1">
         <v>119.878</v>
@@ -2278,266 +2352,266 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>-128.31</v>
+        <v>101.78700000000001</v>
       </c>
       <c r="J29" s="3">
-        <v>43.829000000000001</v>
+        <v>73.668999999999997</v>
       </c>
       <c r="K29" s="3">
-        <v>184.25299999999999</v>
+        <v>135.67500000000001</v>
       </c>
       <c r="L29" s="3">
-        <v>-95.363</v>
+        <v>16.628</v>
       </c>
       <c r="M29" s="3">
-        <v>38.509</v>
+        <v>-134.45099999999999</v>
       </c>
       <c r="N29" s="4">
-        <v>-83.159000000000006</v>
+        <v>11.813000000000001</v>
       </c>
       <c r="O29" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P29" t="s">
         <v>20</v>
       </c>
       <c r="Q29" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R29">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C30" s="1">
-        <v>80.322000000000003</v>
+        <v>119.878</v>
       </c>
       <c r="D30" s="1">
-        <v>287.67599999999999</v>
+        <v>289.12299999999999</v>
       </c>
       <c r="E30" s="1">
-        <v>394.35300000000001</v>
+        <v>498.44400000000002</v>
       </c>
       <c r="F30" s="1">
-        <v>-131.82</v>
+        <v>-90</v>
       </c>
       <c r="G30" s="1">
-        <v>-45.268000000000001</v>
+        <v>-90</v>
       </c>
       <c r="H30" s="1">
-        <v>61.453000000000003</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>29.462</v>
+        <v>26.748999999999999</v>
       </c>
       <c r="J30" s="3">
-        <v>-39.472999999999999</v>
+        <v>81.387</v>
       </c>
       <c r="K30" s="3">
-        <v>-8.3919999999999995</v>
+        <v>117.223</v>
       </c>
       <c r="L30" s="3">
-        <v>117.682</v>
+        <v>114.142</v>
       </c>
       <c r="M30" s="3">
-        <v>85.679000000000002</v>
+        <v>101.88200000000001</v>
       </c>
       <c r="N30" s="4">
-        <v>-119.224</v>
+        <v>155.327</v>
       </c>
       <c r="O30" t="s">
         <v>18</v>
       </c>
       <c r="P30" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q30" t="s">
         <v>2</v>
       </c>
       <c r="R30">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C31" s="1">
-        <v>80.322000000000003</v>
+        <v>119.878</v>
       </c>
       <c r="D31" s="1">
-        <v>287.67599999999999</v>
+        <v>289.12299999999999</v>
       </c>
       <c r="E31" s="1">
-        <v>394.35300000000001</v>
+        <v>498.44400000000002</v>
       </c>
       <c r="F31" s="1">
-        <v>-131.82</v>
+        <v>-90</v>
       </c>
       <c r="G31" s="1">
-        <v>-45.268000000000001</v>
+        <v>-90</v>
       </c>
       <c r="H31" s="1">
-        <v>61.453000000000003</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>-150.53800000000001</v>
+        <v>-78.212999999999994</v>
       </c>
       <c r="J31" s="3">
-        <v>39.472999999999999</v>
+        <v>-73.668999999999997</v>
       </c>
       <c r="K31" s="3">
-        <v>188.392</v>
+        <v>44.325000000000003</v>
       </c>
       <c r="L31" s="3">
-        <v>-62.317999999999998</v>
+        <v>-163.37200000000001</v>
       </c>
       <c r="M31" s="3">
-        <v>85.679000000000002</v>
+        <v>-134.45099999999999</v>
       </c>
       <c r="N31" s="4">
-        <v>-119.224</v>
+        <v>11.813000000000001</v>
       </c>
       <c r="O31" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="s">
         <v>19</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C32" s="1">
-        <v>80.322000000000003</v>
+        <v>119.878</v>
       </c>
       <c r="D32" s="1">
-        <v>287.67599999999999</v>
+        <v>289.12299999999999</v>
       </c>
       <c r="E32" s="1">
-        <v>394.35300000000001</v>
+        <v>498.44400000000002</v>
       </c>
       <c r="F32" s="1">
-        <v>-131.82</v>
+        <v>-90</v>
       </c>
       <c r="G32" s="1">
-        <v>-45.268000000000001</v>
+        <v>-90</v>
       </c>
       <c r="H32" s="1">
-        <v>61.453000000000003</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>35.161999999999999</v>
+        <v>-153.251</v>
       </c>
       <c r="J32" s="3">
-        <v>88.468000000000004</v>
+        <v>-81.387</v>
       </c>
       <c r="K32" s="3">
-        <v>140.15</v>
+        <v>62.777000000000001</v>
       </c>
       <c r="L32" s="3">
-        <v>-108.846</v>
+        <v>-65.858000000000004</v>
       </c>
       <c r="M32" s="3">
-        <v>-111.92</v>
+        <v>101.88200000000001</v>
       </c>
       <c r="N32" s="4">
-        <v>-91.804000000000002</v>
+        <v>155.327</v>
       </c>
       <c r="O32" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P32" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C33" s="1">
-        <v>80.322000000000003</v>
+        <v>119.878</v>
       </c>
       <c r="D33" s="1">
-        <v>287.67599999999999</v>
+        <v>289.12299999999999</v>
       </c>
       <c r="E33" s="1">
-        <v>394.35300000000001</v>
+        <v>498.44400000000002</v>
       </c>
       <c r="F33" s="1">
-        <v>-131.82</v>
+        <v>-90</v>
       </c>
       <c r="G33" s="1">
-        <v>-45.268000000000001</v>
+        <v>-90</v>
       </c>
       <c r="H33" s="1">
-        <v>61.453000000000003</v>
+        <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>-144.839</v>
+        <v>-128.31</v>
       </c>
       <c r="J33" s="3">
-        <v>-88.468000000000004</v>
+        <v>43.829000000000001</v>
       </c>
       <c r="K33" s="3">
-        <v>39.85</v>
+        <v>184.25299999999999</v>
       </c>
       <c r="L33" s="3">
-        <v>71.153999999999996</v>
+        <v>-95.363</v>
       </c>
       <c r="M33" s="3">
-        <v>-111.92</v>
+        <v>38.509</v>
       </c>
       <c r="N33" s="4">
-        <v>-91.804000000000002</v>
+        <v>-83.159000000000006</v>
       </c>
       <c r="O33" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q33" t="s">
         <v>19</v>
       </c>
       <c r="R33">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C34" s="1">
         <v>80.322000000000003</v>
@@ -2558,25 +2632,25 @@
         <v>61.453000000000003</v>
       </c>
       <c r="I34" s="2">
-        <v>78</v>
+        <v>29.462</v>
       </c>
       <c r="J34" s="3">
-        <v>-41</v>
+        <v>-39.472999999999999</v>
       </c>
       <c r="K34" s="3">
-        <v>17</v>
+        <v>-8.3919999999999995</v>
       </c>
       <c r="L34" s="3">
-        <v>-42</v>
+        <v>117.682</v>
       </c>
       <c r="M34" s="3">
-        <v>-60</v>
+        <v>85.679000000000002</v>
       </c>
       <c r="N34" s="4">
-        <v>10</v>
+        <v>-119.224</v>
       </c>
       <c r="O34" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P34" t="s">
         <v>1</v>
@@ -2585,15 +2659,15 @@
         <v>2</v>
       </c>
       <c r="R34">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C35" s="1">
         <v>80.322000000000003</v>
@@ -2614,25 +2688,25 @@
         <v>61.453000000000003</v>
       </c>
       <c r="I35" s="2">
-        <v>-102</v>
+        <v>-150.53800000000001</v>
       </c>
       <c r="J35" s="3">
-        <v>41</v>
+        <v>39.472999999999999</v>
       </c>
       <c r="K35" s="3">
-        <v>163</v>
+        <v>188.392</v>
       </c>
       <c r="L35" s="3">
-        <v>138</v>
+        <v>-62.317999999999998</v>
       </c>
       <c r="M35" s="3">
-        <v>-60</v>
+        <v>85.679000000000002</v>
       </c>
       <c r="N35" s="4">
-        <v>10</v>
+        <v>-119.224</v>
       </c>
       <c r="O35" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P35" t="s">
         <v>20</v>
@@ -2641,15 +2715,15 @@
         <v>19</v>
       </c>
       <c r="R35">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1">
         <v>80.322000000000003</v>
@@ -2670,25 +2744,25 @@
         <v>61.453000000000003</v>
       </c>
       <c r="I36" s="2">
-        <v>44.610999999999997</v>
+        <v>35.161999999999999</v>
       </c>
       <c r="J36" s="3">
-        <v>89.087000000000003</v>
+        <v>88.468000000000004</v>
       </c>
       <c r="K36" s="3">
-        <v>109.193</v>
+        <v>140.15</v>
       </c>
       <c r="L36" s="3">
-        <v>94.703000000000003</v>
+        <v>-108.846</v>
       </c>
       <c r="M36" s="3">
-        <v>121.416</v>
+        <v>-111.92</v>
       </c>
       <c r="N36" s="4">
-        <v>121.782</v>
+        <v>-91.804000000000002</v>
       </c>
       <c r="O36" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P36" t="s">
         <v>20</v>
@@ -2697,15 +2771,15 @@
         <v>2</v>
       </c>
       <c r="R36">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C37" s="1">
         <v>80.322000000000003</v>
@@ -2726,25 +2800,25 @@
         <v>61.453000000000003</v>
       </c>
       <c r="I37" s="2">
-        <v>-135.38900000000001</v>
+        <v>-144.839</v>
       </c>
       <c r="J37" s="3">
-        <v>-89.087000000000003</v>
+        <v>-88.468000000000004</v>
       </c>
       <c r="K37" s="3">
-        <v>70.807000000000002</v>
+        <v>39.85</v>
       </c>
       <c r="L37" s="3">
-        <v>-85.296999999999997</v>
+        <v>71.153999999999996</v>
       </c>
       <c r="M37" s="3">
-        <v>121.416</v>
+        <v>-111.92</v>
       </c>
       <c r="N37" s="4">
-        <v>121.782</v>
+        <v>-91.804000000000002</v>
       </c>
       <c r="O37" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P37" t="s">
         <v>1</v>
@@ -2753,166 +2827,166 @@
         <v>19</v>
       </c>
       <c r="R37">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="1">
+        <v>80.322000000000003</v>
+      </c>
+      <c r="D38" s="1">
+        <v>287.67599999999999</v>
+      </c>
+      <c r="E38" s="1">
+        <v>394.35300000000001</v>
+      </c>
+      <c r="F38" s="1">
+        <v>-131.82</v>
+      </c>
+      <c r="G38" s="1">
+        <v>-45.268000000000001</v>
+      </c>
+      <c r="H38" s="1">
+        <v>61.453000000000003</v>
+      </c>
+      <c r="I38" s="2">
+        <v>78</v>
+      </c>
+      <c r="J38" s="3">
+        <v>-41</v>
+      </c>
+      <c r="K38" s="3">
+        <v>17</v>
+      </c>
+      <c r="L38" s="3">
+        <v>-42</v>
+      </c>
+      <c r="M38" s="3">
+        <v>-60</v>
+      </c>
+      <c r="N38" s="4">
         <v>10</v>
       </c>
-      <c r="B38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="1">
-        <v>600</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
-        <v>100</v>
-      </c>
-      <c r="F38" s="1">
-        <v>-180</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>70</v>
-      </c>
-      <c r="I38" s="2">
-        <v>-14.478</v>
-      </c>
-      <c r="J38" s="3">
-        <v>119.78</v>
-      </c>
-      <c r="K38" s="3">
-        <v>78.001000000000005</v>
-      </c>
-      <c r="L38" s="3">
-        <v>-180</v>
-      </c>
-      <c r="M38" s="3">
-        <v>168.001</v>
-      </c>
-      <c r="N38" s="4">
-        <v>-95.522000000000006</v>
-      </c>
       <c r="O38" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="s">
         <v>2</v>
       </c>
       <c r="R38">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="1">
+        <v>80.322000000000003</v>
+      </c>
+      <c r="D39" s="1">
+        <v>287.67599999999999</v>
+      </c>
+      <c r="E39" s="1">
+        <v>394.35300000000001</v>
+      </c>
+      <c r="F39" s="1">
+        <v>-131.82</v>
+      </c>
+      <c r="G39" s="1">
+        <v>-45.268000000000001</v>
+      </c>
+      <c r="H39" s="1">
+        <v>61.453000000000003</v>
+      </c>
+      <c r="I39" s="2">
+        <v>-102</v>
+      </c>
+      <c r="J39" s="3">
+        <v>41</v>
+      </c>
+      <c r="K39" s="3">
+        <v>163</v>
+      </c>
+      <c r="L39" s="3">
+        <v>138</v>
+      </c>
+      <c r="M39" s="3">
+        <v>-60</v>
+      </c>
+      <c r="N39" s="4">
         <v>10</v>
       </c>
-      <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="1">
-        <v>600</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
-        <v>100</v>
-      </c>
-      <c r="F39" s="1">
-        <v>-180</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>70</v>
-      </c>
-      <c r="I39" s="2">
-        <v>165.52199999999999</v>
-      </c>
-      <c r="J39" s="3">
-        <v>-119.78</v>
-      </c>
-      <c r="K39" s="3">
-        <v>101.999</v>
-      </c>
-      <c r="L39" s="3">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3">
-        <v>168.001</v>
-      </c>
-      <c r="N39" s="4">
-        <v>-95.522000000000006</v>
-      </c>
       <c r="O39" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P39" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q39" t="s">
         <v>19</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C40" s="1">
-        <v>600</v>
+        <v>80.322000000000003</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>287.67599999999999</v>
       </c>
       <c r="E40" s="1">
-        <v>100</v>
+        <v>394.35300000000001</v>
       </c>
       <c r="F40" s="1">
-        <v>-180</v>
+        <v>-131.82</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>-45.268000000000001</v>
       </c>
       <c r="H40" s="1">
-        <v>70</v>
+        <v>61.453000000000003</v>
       </c>
       <c r="I40" s="2">
-        <v>14.478</v>
+        <v>44.610999999999997</v>
       </c>
       <c r="J40" s="3">
-        <v>119.78</v>
+        <v>89.087000000000003</v>
       </c>
       <c r="K40" s="3">
-        <v>78.001000000000005</v>
+        <v>109.193</v>
       </c>
       <c r="L40" s="3">
-        <v>0</v>
+        <v>94.703000000000003</v>
       </c>
       <c r="M40" s="3">
-        <v>-168.001</v>
+        <v>121.416</v>
       </c>
       <c r="N40" s="4">
-        <v>55.521999999999998</v>
+        <v>121.782</v>
       </c>
       <c r="O40" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P40" t="s">
         <v>20</v>
@@ -2921,71 +2995,71 @@
         <v>2</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C41" s="1">
-        <v>600</v>
+        <v>80.322000000000003</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>287.67599999999999</v>
       </c>
       <c r="E41" s="1">
-        <v>100</v>
+        <v>394.35300000000001</v>
       </c>
       <c r="F41" s="1">
-        <v>-180</v>
+        <v>-131.82</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>-45.268000000000001</v>
       </c>
       <c r="H41" s="1">
-        <v>70</v>
+        <v>61.453000000000003</v>
       </c>
       <c r="I41" s="2">
-        <v>14.478</v>
+        <v>-135.38900000000001</v>
       </c>
       <c r="J41" s="3">
-        <v>11.999000000000001</v>
+        <v>-89.087000000000003</v>
       </c>
       <c r="K41" s="3">
-        <v>-29.78</v>
+        <v>70.807000000000002</v>
       </c>
       <c r="L41" s="3">
-        <v>0</v>
+        <v>-85.296999999999997</v>
       </c>
       <c r="M41" s="3">
-        <v>-60.22</v>
+        <v>121.416</v>
       </c>
       <c r="N41" s="4">
-        <v>55.521999999999998</v>
+        <v>121.782</v>
       </c>
       <c r="O41" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P41" t="s">
         <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R41">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C42" s="1">
         <v>600</v>
@@ -3006,42 +3080,42 @@
         <v>70</v>
       </c>
       <c r="I42" s="2">
-        <v>165.52199999999999</v>
+        <v>-14.478</v>
       </c>
       <c r="J42" s="3">
-        <v>-11.999000000000001</v>
+        <v>119.78</v>
       </c>
       <c r="K42" s="3">
-        <v>-150.22</v>
+        <v>78.001000000000005</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="M42" s="3">
-        <v>60.22</v>
+        <v>168.001</v>
       </c>
       <c r="N42" s="4">
         <v>-95.522000000000006</v>
       </c>
       <c r="O42" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P42" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q42" t="s">
         <v>2</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C43" s="1">
         <v>600</v>
@@ -3062,22 +3136,22 @@
         <v>70</v>
       </c>
       <c r="I43" s="2">
-        <v>173.66399999999999</v>
+        <v>165.52199999999999</v>
       </c>
       <c r="J43" s="3">
-        <v>-121.233</v>
+        <v>-119.78</v>
       </c>
       <c r="K43" s="3">
-        <v>90.001000000000005</v>
+        <v>101.999</v>
       </c>
       <c r="L43" s="3">
-        <v>63.811</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
-        <v>179.999</v>
+        <v>168.001</v>
       </c>
       <c r="N43" s="4">
-        <v>-39.860999999999997</v>
+        <v>-95.522000000000006</v>
       </c>
       <c r="O43" t="s">
         <v>18</v>
@@ -3089,15 +3163,15 @@
         <v>19</v>
       </c>
       <c r="R43">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C44" s="1">
         <v>600</v>
@@ -3118,25 +3192,25 @@
         <v>70</v>
       </c>
       <c r="I44" s="2">
-        <v>6.335</v>
+        <v>14.478</v>
       </c>
       <c r="J44" s="3">
-        <v>121.233</v>
+        <v>119.78</v>
       </c>
       <c r="K44" s="3">
-        <v>90</v>
+        <v>78.001000000000005</v>
       </c>
       <c r="L44" s="3">
-        <v>-63.811</v>
+        <v>0</v>
       </c>
       <c r="M44" s="3">
-        <v>179.999</v>
+        <v>-168.001</v>
       </c>
       <c r="N44" s="4">
-        <v>-0.14599999999999999</v>
+        <v>55.521999999999998</v>
       </c>
       <c r="O44" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P44" t="s">
         <v>20</v>
@@ -3145,15 +3219,15 @@
         <v>2</v>
       </c>
       <c r="R44">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C45" s="1">
         <v>600</v>
@@ -3174,7 +3248,7 @@
         <v>70</v>
       </c>
       <c r="I45" s="2">
-        <v>-14.478</v>
+        <v>14.478</v>
       </c>
       <c r="J45" s="3">
         <v>11.999000000000001</v>
@@ -3183,16 +3257,16 @@
         <v>-29.78</v>
       </c>
       <c r="L45" s="3">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="M45" s="3">
-        <v>60.22</v>
+        <v>-60.22</v>
       </c>
       <c r="N45" s="4">
-        <v>-95.522000000000006</v>
+        <v>55.521999999999998</v>
       </c>
       <c r="O45" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P45" t="s">
         <v>1</v>
@@ -3201,15 +3275,15 @@
         <v>2</v>
       </c>
       <c r="R45">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C46" s="1">
         <v>600</v>
@@ -3230,22 +3304,22 @@
         <v>70</v>
       </c>
       <c r="I46" s="2">
-        <v>-165.52199999999999</v>
+        <v>165.52199999999999</v>
       </c>
       <c r="J46" s="3">
-        <v>-119.78</v>
+        <v>-11.999000000000001</v>
       </c>
       <c r="K46" s="3">
-        <v>101.999</v>
+        <v>-150.22</v>
       </c>
       <c r="L46" s="3">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="M46" s="3">
-        <v>-168.01</v>
+        <v>60.22</v>
       </c>
       <c r="N46" s="4">
-        <v>55.521999999999998</v>
+        <v>-95.522000000000006</v>
       </c>
       <c r="O46" t="s">
         <v>0</v>
@@ -3254,18 +3328,18 @@
         <v>1</v>
       </c>
       <c r="Q46" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R46">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C47" s="1">
         <v>600</v>
@@ -3286,25 +3360,25 @@
         <v>70</v>
       </c>
       <c r="I47" s="2">
-        <v>-165.52199999999999</v>
+        <v>173.66399999999999</v>
       </c>
       <c r="J47" s="3">
-        <v>-11.999000000000001</v>
+        <v>-121.233</v>
       </c>
       <c r="K47" s="3">
-        <v>-150.22</v>
+        <v>90.001000000000005</v>
       </c>
       <c r="L47" s="3">
-        <v>180</v>
+        <v>63.811</v>
       </c>
       <c r="M47" s="3">
-        <v>-60.22</v>
+        <v>179.999</v>
       </c>
       <c r="N47" s="4">
-        <v>55.521999999999998</v>
+        <v>-39.860999999999997</v>
       </c>
       <c r="O47" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P47" t="s">
         <v>1</v>
@@ -3313,15 +3387,15 @@
         <v>19</v>
       </c>
       <c r="R47">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C48" s="1">
         <v>600</v>
@@ -3342,16 +3416,16 @@
         <v>70</v>
       </c>
       <c r="I48" s="2">
-        <v>-173.66499999999999</v>
+        <v>6.335</v>
       </c>
       <c r="J48" s="3">
-        <v>-121.233</v>
+        <v>121.233</v>
       </c>
       <c r="K48" s="3">
         <v>90</v>
       </c>
       <c r="L48" s="3">
-        <v>116.19</v>
+        <v>-63.811</v>
       </c>
       <c r="M48" s="3">
         <v>179.999</v>
@@ -3363,21 +3437,21 @@
         <v>18</v>
       </c>
       <c r="P48" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q48" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R48">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C49" s="1">
         <v>600</v>
@@ -3398,78 +3472,78 @@
         <v>70</v>
       </c>
       <c r="I49" s="2">
-        <v>-6.3360000000000003</v>
+        <v>-14.478</v>
       </c>
       <c r="J49" s="3">
-        <v>121.233</v>
+        <v>11.999000000000001</v>
       </c>
       <c r="K49" s="3">
-        <v>89.998999999999995</v>
+        <v>-29.78</v>
       </c>
       <c r="L49" s="3">
-        <v>-116.197</v>
+        <v>-180</v>
       </c>
       <c r="M49" s="3">
-        <v>179.999</v>
+        <v>60.22</v>
       </c>
       <c r="N49" s="4">
-        <v>-39.860999999999997</v>
+        <v>-95.522000000000006</v>
       </c>
       <c r="O49" t="s">
         <v>18</v>
       </c>
       <c r="P49" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="s">
         <v>2</v>
       </c>
       <c r="R49">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C50" s="1">
-        <v>209.47</v>
+        <v>600</v>
       </c>
       <c r="D50" s="1">
-        <v>-42.893999999999998</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>685.49599999999998</v>
+        <v>100</v>
       </c>
       <c r="F50" s="1">
-        <v>-95.378</v>
+        <v>-180</v>
       </c>
       <c r="G50" s="1">
-        <v>-64.225999999999999</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>-56.402000000000001</v>
+        <v>70</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>-165.52199999999999</v>
       </c>
       <c r="J50" s="3">
-        <v>-45</v>
+        <v>-119.78</v>
       </c>
       <c r="K50" s="3">
-        <v>44</v>
+        <v>101.999</v>
       </c>
       <c r="L50" s="3">
-        <v>-37</v>
+        <v>-180</v>
       </c>
       <c r="M50" s="3">
-        <v>-53</v>
+        <v>-168.01</v>
       </c>
       <c r="N50" s="4">
-        <v>0</v>
+        <v>55.521999999999998</v>
       </c>
       <c r="O50" t="s">
         <v>0</v>
@@ -3478,113 +3552,113 @@
         <v>1</v>
       </c>
       <c r="Q50" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R50">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C51" s="1">
-        <v>209.47</v>
+        <v>600</v>
       </c>
       <c r="D51" s="1">
-        <v>-42.893999999999998</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>685.49599999999998</v>
+        <v>100</v>
       </c>
       <c r="F51" s="1">
-        <v>-95.378</v>
+        <v>-180</v>
       </c>
       <c r="G51" s="1">
-        <v>-64.225999999999999</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>-56.402000000000001</v>
+        <v>70</v>
       </c>
       <c r="I51" s="2">
-        <v>11.855</v>
+        <v>-165.52199999999999</v>
       </c>
       <c r="J51" s="3">
-        <v>54.151000000000003</v>
+        <v>-11.999000000000001</v>
       </c>
       <c r="K51" s="3">
-        <v>144.00700000000001</v>
+        <v>-150.22</v>
       </c>
       <c r="L51" s="3">
-        <v>-28.773</v>
+        <v>180</v>
       </c>
       <c r="M51" s="3">
-        <v>-142.88900000000001</v>
+        <v>-60.22</v>
       </c>
       <c r="N51" s="4">
-        <v>-48.616</v>
+        <v>55.521999999999998</v>
       </c>
       <c r="O51" t="s">
         <v>0</v>
       </c>
       <c r="P51" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R51">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C52" s="1">
-        <v>209.47</v>
+        <v>600</v>
       </c>
       <c r="D52" s="1">
-        <v>-42.893999999999998</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>685.49599999999998</v>
+        <v>100</v>
       </c>
       <c r="F52" s="1">
-        <v>-95.378</v>
+        <v>-180</v>
       </c>
       <c r="G52" s="1">
-        <v>-64.225999999999999</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>-56.402000000000001</v>
+        <v>70</v>
       </c>
       <c r="I52" s="2">
-        <v>47.115000000000002</v>
+        <v>-173.66499999999999</v>
       </c>
       <c r="J52" s="3">
-        <v>-53.923999999999999</v>
+        <v>-121.233</v>
       </c>
       <c r="K52" s="3">
-        <v>35.921999999999997</v>
+        <v>90</v>
       </c>
       <c r="L52" s="3">
-        <v>28.105</v>
+        <v>116.19</v>
       </c>
       <c r="M52" s="3">
-        <v>-41.923999999999999</v>
+        <v>179.999</v>
       </c>
       <c r="N52" s="4">
-        <v>-48.121000000000002</v>
+        <v>-0.14599999999999999</v>
       </c>
       <c r="O52" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P52" t="s">
         <v>1</v>
@@ -3593,71 +3667,71 @@
         <v>19</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C53" s="1">
-        <v>209.47</v>
+        <v>600</v>
       </c>
       <c r="D53" s="1">
-        <v>-42.893999999999998</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>685.49599999999998</v>
+        <v>100</v>
       </c>
       <c r="F53" s="1">
-        <v>-95.378</v>
+        <v>-180</v>
       </c>
       <c r="G53" s="1">
-        <v>-64.225999999999999</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>-56.402000000000001</v>
+        <v>70</v>
       </c>
       <c r="I53" s="2">
-        <v>49.247</v>
+        <v>-6.3360000000000003</v>
       </c>
       <c r="J53" s="3">
-        <v>46.825000000000003</v>
+        <v>121.233</v>
       </c>
       <c r="K53" s="3">
-        <v>135.95400000000001</v>
+        <v>89.998999999999995</v>
       </c>
       <c r="L53" s="3">
-        <v>29.379000000000001</v>
+        <v>-116.197</v>
       </c>
       <c r="M53" s="3">
-        <v>-134.512</v>
+        <v>179.999</v>
       </c>
       <c r="N53" s="4">
-        <v>-5.01</v>
+        <v>-39.860999999999997</v>
       </c>
       <c r="O53" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q53" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="R53">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C54" s="1">
         <v>209.47</v>
@@ -3678,22 +3752,22 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I54" s="2">
-        <v>116.682</v>
+        <v>0</v>
       </c>
       <c r="J54" s="3">
-        <v>-62.683999999999997</v>
+        <v>-45</v>
       </c>
       <c r="K54" s="3">
-        <v>36.936</v>
+        <v>44</v>
       </c>
       <c r="L54" s="3">
-        <v>86.888999999999996</v>
+        <v>-37</v>
       </c>
       <c r="M54" s="3">
-        <v>-89.75</v>
+        <v>-53</v>
       </c>
       <c r="N54" s="4">
-        <v>-78.691000000000003</v>
+        <v>0</v>
       </c>
       <c r="O54" t="s">
         <v>0</v>
@@ -3702,18 +3776,18 @@
         <v>1</v>
       </c>
       <c r="Q54" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R54">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C55" s="1">
         <v>209.47</v>
@@ -3734,42 +3808,42 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I55" s="2">
-        <v>117.84399999999999</v>
+        <v>11.855</v>
       </c>
       <c r="J55" s="3">
-        <v>40.094000000000001</v>
+        <v>54.151000000000003</v>
       </c>
       <c r="K55" s="3">
-        <v>165.667</v>
+        <v>144.00700000000001</v>
       </c>
       <c r="L55" s="3">
-        <v>-87.960999999999999</v>
+        <v>-28.773</v>
       </c>
       <c r="M55" s="3">
-        <v>91.457999999999998</v>
+        <v>-142.88900000000001</v>
       </c>
       <c r="N55" s="4">
-        <v>-129.964</v>
+        <v>-48.616</v>
       </c>
       <c r="O55" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P55" t="s">
         <v>20</v>
       </c>
       <c r="Q55" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R55">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C56" s="1">
         <v>209.47</v>
@@ -3790,25 +3864,25 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I56" s="2">
-        <v>119.875</v>
+        <v>47.115000000000002</v>
       </c>
       <c r="J56" s="3">
-        <v>-62.707000000000001</v>
+        <v>-53.923999999999999</v>
       </c>
       <c r="K56" s="3">
-        <v>67.984999999999999</v>
+        <v>35.921999999999997</v>
       </c>
       <c r="L56" s="3">
-        <v>-89.834999999999994</v>
+        <v>28.105</v>
       </c>
       <c r="M56" s="3">
-        <v>92.585999999999999</v>
+        <v>-41.923999999999999</v>
       </c>
       <c r="N56" s="4">
-        <v>132.291</v>
+        <v>-48.121000000000002</v>
       </c>
       <c r="O56" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P56" t="s">
         <v>1</v>
@@ -3817,15 +3891,15 @@
         <v>19</v>
       </c>
       <c r="R56">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C57" s="1">
         <v>209.47</v>
@@ -3846,42 +3920,42 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I57" s="2">
-        <v>132.631</v>
+        <v>49.247</v>
       </c>
       <c r="J57" s="3">
-        <v>40.31</v>
+        <v>46.825000000000003</v>
       </c>
       <c r="K57" s="3">
-        <v>134.72800000000001</v>
+        <v>135.95400000000001</v>
       </c>
       <c r="L57" s="3">
-        <v>101.59</v>
+        <v>29.379000000000001</v>
       </c>
       <c r="M57" s="3">
-        <v>-81.968999999999994</v>
+        <v>-134.512</v>
       </c>
       <c r="N57" s="4">
-        <v>17.952000000000002</v>
+        <v>-5.01</v>
       </c>
       <c r="O57" t="s">
         <v>0</v>
       </c>
       <c r="P57" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q57" t="s">
         <v>20</v>
       </c>
-      <c r="Q57" t="s">
-        <v>19</v>
-      </c>
       <c r="R57">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C58" s="1">
         <v>209.47</v>
@@ -3902,22 +3976,22 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I58" s="2">
-        <v>-130.75299999999999</v>
+        <v>116.682</v>
       </c>
       <c r="J58" s="3">
-        <v>-46.825000000000003</v>
+        <v>-62.683999999999997</v>
       </c>
       <c r="K58" s="3">
-        <v>44.045999999999999</v>
+        <v>36.936</v>
       </c>
       <c r="L58" s="3">
-        <v>-150.62100000000001</v>
+        <v>86.888999999999996</v>
       </c>
       <c r="M58" s="3">
-        <v>-134.512</v>
+        <v>-89.75</v>
       </c>
       <c r="N58" s="4">
-        <v>-5.01</v>
+        <v>-78.691000000000003</v>
       </c>
       <c r="O58" t="s">
         <v>0</v>
@@ -3926,18 +4000,18 @@
         <v>1</v>
       </c>
       <c r="Q58" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R58">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C59" s="1">
         <v>209.47</v>
@@ -3958,42 +4032,42 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I59" s="2">
-        <v>-132.88499999999999</v>
+        <v>117.84399999999999</v>
       </c>
       <c r="J59" s="3">
-        <v>53.923999999999999</v>
+        <v>40.094000000000001</v>
       </c>
       <c r="K59" s="3">
-        <v>144.078</v>
+        <v>165.667</v>
       </c>
       <c r="L59" s="3">
-        <v>-151.89500000000001</v>
+        <v>-87.960999999999999</v>
       </c>
       <c r="M59" s="3">
-        <v>-41.923999999999999</v>
+        <v>91.457999999999998</v>
       </c>
       <c r="N59" s="4">
-        <v>-48.121000000000002</v>
+        <v>-129.964</v>
       </c>
       <c r="O59" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P59" t="s">
         <v>20</v>
       </c>
       <c r="Q59" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R59">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C60" s="1">
         <v>209.47</v>
@@ -4014,25 +4088,25 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I60" s="2">
-        <v>-168.14500000000001</v>
+        <v>119.875</v>
       </c>
       <c r="J60" s="3">
-        <v>-54.151000000000003</v>
+        <v>-62.707000000000001</v>
       </c>
       <c r="K60" s="3">
-        <v>35.993000000000002</v>
+        <v>67.984999999999999</v>
       </c>
       <c r="L60" s="3">
-        <v>151.227</v>
+        <v>-89.834999999999994</v>
       </c>
       <c r="M60" s="3">
-        <v>-142.88900000000001</v>
+        <v>92.585999999999999</v>
       </c>
       <c r="N60" s="4">
-        <v>-48.616</v>
+        <v>132.291</v>
       </c>
       <c r="O60" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P60" t="s">
         <v>1</v>
@@ -4041,15 +4115,15 @@
         <v>19</v>
       </c>
       <c r="R60">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C61" s="1">
         <v>209.47</v>
@@ -4070,22 +4144,22 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I61" s="2">
-        <v>-180</v>
+        <v>132.631</v>
       </c>
       <c r="J61" s="3">
-        <v>45</v>
+        <v>40.31</v>
       </c>
       <c r="K61" s="3">
-        <v>136</v>
+        <v>134.72800000000001</v>
       </c>
       <c r="L61" s="3">
-        <v>143</v>
+        <v>101.59</v>
       </c>
       <c r="M61" s="3">
-        <v>-53</v>
+        <v>-81.968999999999994</v>
       </c>
       <c r="N61" s="4">
-        <v>0</v>
+        <v>17.952000000000002</v>
       </c>
       <c r="O61" t="s">
         <v>0</v>
@@ -4097,15 +4171,15 @@
         <v>19</v>
       </c>
       <c r="R61">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C62" s="1">
         <v>209.47</v>
@@ -4126,22 +4200,22 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I62" s="2">
-        <v>-47.369</v>
+        <v>-130.75299999999999</v>
       </c>
       <c r="J62" s="3">
-        <v>-40.31</v>
+        <v>-46.825000000000003</v>
       </c>
       <c r="K62" s="3">
-        <v>45.271999999999998</v>
+        <v>44.045999999999999</v>
       </c>
       <c r="L62" s="3">
-        <v>-78.41</v>
+        <v>-150.62100000000001</v>
       </c>
       <c r="M62" s="3">
-        <v>-81.968999999999994</v>
+        <v>-134.512</v>
       </c>
       <c r="N62" s="4">
-        <v>17.952000000000002</v>
+        <v>-5.01</v>
       </c>
       <c r="O62" t="s">
         <v>0</v>
@@ -4153,15 +4227,15 @@
         <v>2</v>
       </c>
       <c r="R62">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C63" s="1">
         <v>209.47</v>
@@ -4182,25 +4256,25 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I63" s="2">
-        <v>-60.125</v>
+        <v>-132.88499999999999</v>
       </c>
       <c r="J63" s="3">
-        <v>62.707000000000001</v>
+        <v>53.923999999999999</v>
       </c>
       <c r="K63" s="3">
-        <v>112.015</v>
+        <v>144.078</v>
       </c>
       <c r="L63" s="3">
-        <v>90.165000000000006</v>
+        <v>-151.89500000000001</v>
       </c>
       <c r="M63" s="3">
-        <v>92.585999999999999</v>
+        <v>-41.923999999999999</v>
       </c>
       <c r="N63" s="4">
-        <v>132.291</v>
+        <v>-48.121000000000002</v>
       </c>
       <c r="O63" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P63" t="s">
         <v>20</v>
@@ -4209,15 +4283,15 @@
         <v>2</v>
       </c>
       <c r="R63">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C64" s="1">
         <v>209.47</v>
@@ -4238,42 +4312,42 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I64" s="2">
-        <v>-62.155999999999999</v>
+        <v>-168.14500000000001</v>
       </c>
       <c r="J64" s="3">
-        <v>-40.094000000000001</v>
+        <v>-54.151000000000003</v>
       </c>
       <c r="K64" s="3">
-        <v>14.333</v>
+        <v>35.993000000000002</v>
       </c>
       <c r="L64" s="3">
-        <v>92.039000000000001</v>
+        <v>151.227</v>
       </c>
       <c r="M64" s="3">
-        <v>91.457999999999998</v>
+        <v>-142.88900000000001</v>
       </c>
       <c r="N64" s="4">
-        <v>-129.964</v>
+        <v>-48.616</v>
       </c>
       <c r="O64" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P64" t="s">
         <v>1</v>
       </c>
       <c r="Q64" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R64">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C65" s="1">
         <v>209.47</v>
@@ -4294,22 +4368,22 @@
         <v>-56.402000000000001</v>
       </c>
       <c r="I65" s="2">
-        <v>-63.317999999999998</v>
+        <v>-180</v>
       </c>
       <c r="J65" s="3">
-        <v>62.683999999999997</v>
+        <v>45</v>
       </c>
       <c r="K65" s="3">
-        <v>143.06399999999999</v>
+        <v>136</v>
       </c>
       <c r="L65" s="3">
-        <v>-93.111000000000004</v>
+        <v>143</v>
       </c>
       <c r="M65" s="3">
-        <v>-89.75</v>
+        <v>-53</v>
       </c>
       <c r="N65" s="4">
-        <v>-78.691000000000003</v>
+        <v>0</v>
       </c>
       <c r="O65" t="s">
         <v>0</v>
@@ -4318,54 +4392,54 @@
         <v>20</v>
       </c>
       <c r="Q65" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R65">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C66" s="1">
-        <v>600</v>
+        <v>209.47</v>
       </c>
       <c r="D66" s="1">
-        <v>-150</v>
+        <v>-42.893999999999998</v>
       </c>
       <c r="E66" s="1">
-        <v>540</v>
+        <v>685.49599999999998</v>
       </c>
       <c r="F66" s="1">
-        <v>-180</v>
+        <v>-95.378</v>
       </c>
       <c r="G66" s="1">
-        <v>-90</v>
+        <v>-64.225999999999999</v>
       </c>
       <c r="H66" s="1">
-        <v>0</v>
+        <v>-56.402000000000001</v>
       </c>
       <c r="I66" s="2">
-        <v>0</v>
+        <v>-47.369</v>
       </c>
       <c r="J66" s="3">
-        <v>-10.663</v>
+        <v>-40.31</v>
       </c>
       <c r="K66" s="3">
-        <v>0.99</v>
+        <v>45.271999999999998</v>
       </c>
       <c r="L66" s="3">
-        <v>0</v>
+        <v>-78.41</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.99</v>
+        <v>-81.968999999999994</v>
       </c>
       <c r="N66" s="4">
-        <v>0</v>
+        <v>17.952000000000002</v>
       </c>
       <c r="O66" t="s">
         <v>0</v>
@@ -4377,110 +4451,110 @@
         <v>2</v>
       </c>
       <c r="R66">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C67" s="1">
-        <v>800</v>
+        <v>209.47</v>
       </c>
       <c r="D67" s="1">
-        <v>-150</v>
+        <v>-42.893999999999998</v>
       </c>
       <c r="E67" s="1">
-        <v>540</v>
+        <v>685.49599999999998</v>
       </c>
       <c r="F67" s="1">
-        <v>180</v>
+        <v>-95.378</v>
       </c>
       <c r="G67" s="1">
-        <v>-90</v>
+        <v>-64.225999999999999</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <v>-56.402000000000001</v>
       </c>
       <c r="I67" s="2">
-        <v>0</v>
+        <v>-60.125</v>
       </c>
       <c r="J67" s="3">
-        <v>10.680999999999999</v>
+        <v>62.707000000000001</v>
       </c>
       <c r="K67" s="3">
-        <v>0.99299999999999999</v>
+        <v>112.015</v>
       </c>
       <c r="L67" s="3">
-        <v>0</v>
+        <v>90.165000000000006</v>
       </c>
       <c r="M67" s="3">
-        <v>-0.99299999999999999</v>
+        <v>92.585999999999999</v>
       </c>
       <c r="N67" s="4">
-        <v>0</v>
+        <v>132.291</v>
       </c>
       <c r="O67" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P67" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q67" t="s">
         <v>2</v>
       </c>
       <c r="R67">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B68" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C68" s="1">
-        <v>793.77</v>
+        <v>209.47</v>
       </c>
       <c r="D68" s="1">
-        <v>-150</v>
+        <v>-42.893999999999998</v>
       </c>
       <c r="E68" s="1">
-        <v>531.79600000000005</v>
+        <v>685.49599999999998</v>
       </c>
       <c r="F68" s="1">
-        <v>180</v>
+        <v>-95.378</v>
       </c>
       <c r="G68" s="1">
-        <v>-90</v>
+        <v>-64.225999999999999</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>-56.402000000000001</v>
       </c>
       <c r="I68" s="2">
-        <v>0</v>
+        <v>-62.155999999999999</v>
       </c>
       <c r="J68" s="3">
-        <v>10</v>
+        <v>-40.094000000000001</v>
       </c>
       <c r="K68" s="3">
-        <v>0</v>
+        <v>14.333</v>
       </c>
       <c r="L68" s="3">
-        <v>0</v>
+        <v>92.039000000000001</v>
       </c>
       <c r="M68" s="3">
-        <v>0</v>
+        <v>91.457999999999998</v>
       </c>
       <c r="N68" s="4">
-        <v>0</v>
+        <v>-129.964</v>
       </c>
       <c r="O68" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P68" t="s">
         <v>1</v>
@@ -4489,7 +4563,7 @@
         <v>2</v>
       </c>
       <c r="R68">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -4497,55 +4571,55 @@
         <v>15</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C69" s="1">
-        <v>606.23</v>
+        <v>209.47</v>
       </c>
       <c r="D69" s="1">
-        <v>-150</v>
+        <v>-42.893999999999998</v>
       </c>
       <c r="E69" s="1">
-        <v>531.79600000000005</v>
+        <v>685.49599999999998</v>
       </c>
       <c r="F69" s="1">
-        <v>180</v>
+        <v>-95.378</v>
       </c>
       <c r="G69" s="1">
-        <v>-90</v>
+        <v>-64.225999999999999</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>-56.402000000000001</v>
       </c>
       <c r="I69" s="2">
-        <v>0</v>
+        <v>-63.317999999999998</v>
       </c>
       <c r="J69" s="3">
-        <v>-10</v>
+        <v>62.683999999999997</v>
       </c>
       <c r="K69" s="3">
-        <v>0</v>
+        <v>143.06399999999999</v>
       </c>
       <c r="L69" s="3">
-        <v>0</v>
+        <v>-93.111000000000004</v>
       </c>
       <c r="M69" s="3">
-        <v>0</v>
+        <v>-89.75</v>
       </c>
       <c r="N69" s="4">
-        <v>0</v>
+        <v>-78.691000000000003</v>
       </c>
       <c r="O69" t="s">
         <v>0</v>
       </c>
       <c r="P69" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q69" t="s">
         <v>2</v>
       </c>
       <c r="R69">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -4553,40 +4627,40 @@
         <v>16</v>
       </c>
       <c r="B70" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C70" s="1">
-        <v>783.13499999999999</v>
+        <v>600</v>
       </c>
       <c r="D70" s="1">
         <v>-150</v>
       </c>
       <c r="E70" s="1">
-        <v>653.35</v>
+        <v>540</v>
       </c>
       <c r="F70" s="1">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="G70" s="1">
-        <v>-80</v>
+        <v>-90</v>
       </c>
       <c r="H70" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I70" s="2">
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>10</v>
+        <v>-10.663</v>
       </c>
       <c r="K70" s="3">
-        <v>10</v>
+        <v>0.99</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="N70" s="4">
         <v>0</v>
@@ -4609,22 +4683,22 @@
         <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C71" s="1">
-        <v>783.13499999999999</v>
+        <v>800</v>
       </c>
       <c r="D71" s="1">
         <v>-150</v>
       </c>
       <c r="E71" s="1">
-        <v>410.24200000000002</v>
+        <v>540</v>
       </c>
       <c r="F71" s="1">
         <v>180</v>
       </c>
       <c r="G71" s="1">
-        <v>-80</v>
+        <v>-90</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -4633,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="J71" s="3">
-        <v>10</v>
+        <v>10.680999999999999</v>
       </c>
       <c r="K71" s="3">
-        <v>-10</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="L71" s="3">
         <v>0</v>
       </c>
       <c r="M71" s="3">
-        <v>0</v>
+        <v>-0.99299999999999999</v>
       </c>
       <c r="N71" s="4">
         <v>0</v>
@@ -4665,34 +4739,34 @@
         <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C72" s="1">
-        <v>595.59500000000003</v>
+        <v>793.77</v>
       </c>
       <c r="D72" s="1">
         <v>-150</v>
       </c>
       <c r="E72" s="1">
-        <v>653.35</v>
+        <v>531.79600000000005</v>
       </c>
       <c r="F72" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G72" s="1">
-        <v>-80</v>
+        <v>-90</v>
       </c>
       <c r="H72" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="I72" s="2">
         <v>0</v>
       </c>
       <c r="J72" s="3">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="K72" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
@@ -4721,22 +4795,22 @@
         <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C73" s="1">
-        <v>595.59500000000003</v>
+        <v>606.23</v>
       </c>
       <c r="D73" s="1">
         <v>-150</v>
       </c>
       <c r="E73" s="1">
-        <v>410.24200000000002</v>
+        <v>531.79600000000005</v>
       </c>
       <c r="F73" s="1">
         <v>180</v>
       </c>
       <c r="G73" s="1">
-        <v>-80</v>
+        <v>-90</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -4748,28 +4822,644 @@
         <v>-10</v>
       </c>
       <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="4">
+        <v>0</v>
+      </c>
+      <c r="O73" t="s">
+        <v>0</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>2</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>20</v>
+      </c>
+      <c r="B74" t="s">
+        <v>37</v>
+      </c>
+      <c r="C74" s="1">
+        <v>783.13499999999999</v>
+      </c>
+      <c r="D74" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E74" s="1">
+        <v>653.35</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>-80</v>
+      </c>
+      <c r="H74" s="1">
+        <v>180</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
+        <v>10</v>
+      </c>
+      <c r="K74" s="3">
+        <v>10</v>
+      </c>
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="4">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
+        <v>0</v>
+      </c>
+      <c r="P74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>2</v>
+      </c>
+      <c r="R74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>21</v>
+      </c>
+      <c r="B75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C75" s="1">
+        <v>783.13499999999999</v>
+      </c>
+      <c r="D75" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E75" s="1">
+        <v>410.24200000000002</v>
+      </c>
+      <c r="F75" s="1">
+        <v>180</v>
+      </c>
+      <c r="G75" s="1">
+        <v>-80</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3">
+        <v>10</v>
+      </c>
+      <c r="K75" s="3">
         <v>-10</v>
       </c>
-      <c r="L73" s="3">
-        <v>0</v>
-      </c>
-      <c r="M73" s="3">
-        <v>0</v>
-      </c>
-      <c r="N73" s="4">
-        <v>0</v>
-      </c>
-      <c r="O73" t="s">
-        <v>0</v>
-      </c>
-      <c r="P73" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>2</v>
-      </c>
-      <c r="R73">
-        <v>1</v>
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="4">
+        <v>0</v>
+      </c>
+      <c r="O75" t="s">
+        <v>0</v>
+      </c>
+      <c r="P75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>2</v>
+      </c>
+      <c r="R75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>22</v>
+      </c>
+      <c r="B76" t="s">
+        <v>39</v>
+      </c>
+      <c r="C76" s="1">
+        <v>595.59500000000003</v>
+      </c>
+      <c r="D76" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E76" s="1">
+        <v>653.35</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>-80</v>
+      </c>
+      <c r="H76" s="1">
+        <v>180</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-10</v>
+      </c>
+      <c r="K76" s="3">
+        <v>10</v>
+      </c>
+      <c r="L76" s="3">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3">
+        <v>0</v>
+      </c>
+      <c r="N76" s="4">
+        <v>0</v>
+      </c>
+      <c r="O76" t="s">
+        <v>0</v>
+      </c>
+      <c r="P76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>2</v>
+      </c>
+      <c r="R76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>23</v>
+      </c>
+      <c r="B77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C77" s="1">
+        <v>595.59500000000003</v>
+      </c>
+      <c r="D77" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E77" s="1">
+        <v>410.24200000000002</v>
+      </c>
+      <c r="F77" s="1">
+        <v>180</v>
+      </c>
+      <c r="G77" s="1">
+        <v>-80</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3">
+        <v>-10</v>
+      </c>
+      <c r="K77" s="3">
+        <v>-10</v>
+      </c>
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="4">
+        <v>0</v>
+      </c>
+      <c r="O77" t="s">
+        <v>0</v>
+      </c>
+      <c r="P77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>2</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>24</v>
+      </c>
+      <c r="B78" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="1">
+        <v>214.339</v>
+      </c>
+      <c r="D78" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E78" s="1">
+        <v>498.62900000000002</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>-72.811000000000007</v>
+      </c>
+      <c r="H78" s="1">
+        <v>180</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3">
+        <v>-57.295999999999999</v>
+      </c>
+      <c r="K78" s="3">
+        <v>17.189</v>
+      </c>
+      <c r="L78" s="3">
+        <v>0</v>
+      </c>
+      <c r="M78" s="3">
+        <v>0</v>
+      </c>
+      <c r="N78" s="4">
+        <v>0</v>
+      </c>
+      <c r="O78" t="s">
+        <v>0</v>
+      </c>
+      <c r="P78" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>2</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>24</v>
+      </c>
+      <c r="B79" t="s">
+        <v>73</v>
+      </c>
+      <c r="C79" s="1">
+        <v>214.339</v>
+      </c>
+      <c r="D79" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E79" s="1">
+        <v>498.62900000000002</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>-72.811000000000007</v>
+      </c>
+      <c r="H79" s="1">
+        <v>180</v>
+      </c>
+      <c r="I79" s="2">
+        <v>214.339</v>
+      </c>
+      <c r="J79" s="3">
+        <v>-150</v>
+      </c>
+      <c r="K79" s="3">
+        <v>498.62900000000002</v>
+      </c>
+      <c r="L79" s="3">
+        <v>0</v>
+      </c>
+      <c r="M79" s="3">
+        <v>-72.811000000000007</v>
+      </c>
+      <c r="N79" s="4">
+        <v>180</v>
+      </c>
+      <c r="O79" t="s">
+        <v>0</v>
+      </c>
+      <c r="P79" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>2</v>
+      </c>
+      <c r="R79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>24</v>
+      </c>
+      <c r="B80" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" s="1">
+        <v>214.339</v>
+      </c>
+      <c r="D80" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E80" s="1">
+        <v>498.62900000000002</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>-72.811000000000007</v>
+      </c>
+      <c r="H80" s="1">
+        <v>180</v>
+      </c>
+      <c r="I80" s="2">
+        <v>101.44</v>
+      </c>
+      <c r="J80" s="3">
+        <v>46.902000000000001</v>
+      </c>
+      <c r="K80" s="3">
+        <v>156.31899999999999</v>
+      </c>
+      <c r="L80" s="3">
+        <v>78.263000000000005</v>
+      </c>
+      <c r="M80" s="3">
+        <v>-73.009</v>
+      </c>
+      <c r="N80" s="4">
+        <v>69.813000000000002</v>
+      </c>
+      <c r="O80" t="s">
+        <v>0</v>
+      </c>
+      <c r="P80" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>19</v>
+      </c>
+      <c r="R80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>24</v>
+      </c>
+      <c r="B81" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" s="1">
+        <v>214.339</v>
+      </c>
+      <c r="D81" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E81" s="1">
+        <v>498.62900000000002</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>-72.811000000000007</v>
+      </c>
+      <c r="H81" s="1">
+        <v>180</v>
+      </c>
+      <c r="I81" s="2">
+        <v>138.821</v>
+      </c>
+      <c r="J81" s="3">
+        <v>48.277999999999999</v>
+      </c>
+      <c r="K81" s="3">
+        <v>184.14699999999999</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-118.867</v>
+      </c>
+      <c r="M81" s="3">
+        <v>45.91</v>
+      </c>
+      <c r="N81" s="4">
+        <v>-66.105000000000004</v>
+      </c>
+      <c r="O81" t="s">
+        <v>18</v>
+      </c>
+      <c r="P81" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>19</v>
+      </c>
+      <c r="R81">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>24</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82" s="1">
+        <v>214.339</v>
+      </c>
+      <c r="D82" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E82" s="1">
+        <v>498.62900000000002</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>-72.811000000000007</v>
+      </c>
+      <c r="H82" s="1">
+        <v>180</v>
+      </c>
+      <c r="I82" s="2">
+        <v>98.167000000000002</v>
+      </c>
+      <c r="J82" s="3">
+        <v>-85.501999999999995</v>
+      </c>
+      <c r="K82" s="3">
+        <v>62.02</v>
+      </c>
+      <c r="L82" s="3">
+        <v>-74.710999999999999</v>
+      </c>
+      <c r="M82" s="3">
+        <v>78.62</v>
+      </c>
+      <c r="N82" s="4">
+        <v>151.72499999999999</v>
+      </c>
+      <c r="O82" t="s">
+        <v>18</v>
+      </c>
+      <c r="P82" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>19</v>
+      </c>
+      <c r="R82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83" s="1">
+        <v>700</v>
+      </c>
+      <c r="D83" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E83" s="1">
+        <v>540</v>
+      </c>
+      <c r="F83" s="1">
+        <v>155</v>
+      </c>
+      <c r="G83" s="1">
+        <v>-90</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2">
+        <v>-22.962</v>
+      </c>
+      <c r="J83" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="K83" s="3">
+        <v>-5.5119999999999996</v>
+      </c>
+      <c r="L83" s="3">
+        <v>159.66999999999999</v>
+      </c>
+      <c r="M83" s="3">
+        <v>-5.8760000000000003</v>
+      </c>
+      <c r="N83" s="4">
+        <v>-159.768</v>
+      </c>
+      <c r="O83" t="s">
+        <v>0</v>
+      </c>
+      <c r="P83" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>2</v>
+      </c>
+      <c r="R83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" s="1">
+        <v>700</v>
+      </c>
+      <c r="D84" s="1">
+        <v>-150</v>
+      </c>
+      <c r="E84" s="1">
+        <v>540</v>
+      </c>
+      <c r="F84" s="1">
+        <v>155</v>
+      </c>
+      <c r="G84" s="1">
+        <v>-90</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="2">
+        <v>-22.962</v>
+      </c>
+      <c r="J84" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="K84" s="3">
+        <v>5.5119999999999996</v>
+      </c>
+      <c r="L84" s="3">
+        <v>-159.66999999999999</v>
+      </c>
+      <c r="M84" s="3">
+        <v>5.8760000000000003</v>
+      </c>
+      <c r="N84" s="4">
+        <v>159.768</v>
+      </c>
+      <c r="O84" t="s">
+        <v>18</v>
+      </c>
+      <c r="P84" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>2</v>
+      </c>
+      <c r="R84">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4779,4 +5469,638 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C380FB7D-45D1-4862-84E2-F36B6C026589}">
+  <dimension ref="A1:S24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>-57.295780000000001</v>
+      </c>
+      <c r="P3" s="1">
+        <v>17.18873</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" s="1">
+        <v>68.754940000000005</v>
+      </c>
+      <c r="O4" s="1">
+        <v>40.107050000000001</v>
+      </c>
+      <c r="P4" s="1">
+        <v>-22.918310000000002</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>-57.295780000000001</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>114.59156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>5.7299999999999997E-5</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>-5.7299999999999997E-5</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>52</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>5.7295779999999998E-2</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>-5.7295779999999998E-2</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>180</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="1">
+        <v>57.295780000000001</v>
+      </c>
+      <c r="O10" s="1">
+        <v>-28.64789</v>
+      </c>
+      <c r="P10" s="1">
+        <v>14.32394</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>45.836620000000003</v>
+      </c>
+      <c r="R10" s="1">
+        <v>180</v>
+      </c>
+      <c r="S10" s="1">
+        <v>-74.48451</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>180.05729578</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>179.94270422</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="H13" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>90</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>22.918310000000002</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="1">
+        <v>28.64789</v>
+      </c>
+      <c r="O14" s="1">
+        <v>-40.107050000000001</v>
+      </c>
+      <c r="P14" s="1">
+        <v>90</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>68.754940000000005</v>
+      </c>
+      <c r="R14" s="1">
+        <v>-51.566200000000002</v>
+      </c>
+      <c r="S14" s="1">
+        <v>17.18873</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>90.057295780000004</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>22.918310000000002</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>89.942704219999996</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>22.918310000000002</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>-90</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>22.918310000000002</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="H18" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="1">
+        <v>-45.836620000000003</v>
+      </c>
+      <c r="O18" s="1">
+        <v>34.377470000000002</v>
+      </c>
+      <c r="P18" s="1">
+        <v>-90</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>-22.918310000000002</v>
+      </c>
+      <c r="R18" s="1">
+        <v>63.025359999999999</v>
+      </c>
+      <c r="S18" s="1">
+        <v>-114.59156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="H19" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>-89.942704219999996</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>22.918310000000002</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>-90.057295780000004</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>22.918310000000002</v>
+      </c>
+      <c r="S20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>90</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="H22" t="s">
+        <v>64</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>-90</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>180</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="H23" t="s">
+        <v>65</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>89.942704219999996</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>5.7295779999999998E-2</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="H24" t="s">
+        <v>66</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>-89.942704219999996</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>179.94270422</v>
+      </c>
+      <c r="S24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>